--- a/bonds.xlsx
+++ b/bonds.xlsx
@@ -23,9 +23,9 @@
     <numFmt numFmtId="165" formatCode="[$-419]mmmm\ yyyy;@"/>
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="169" formatCode="DD.MM.YYYY"/>
-    <numFmt numFmtId="170" formatCode="# ##0,00 ₽"/>
+    <numFmt numFmtId="168" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="169" formatCode="# ##0,00 ₽"/>
+    <numFmt numFmtId="170" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -83,7 +83,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -133,8 +133,8 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -150,6 +150,8 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -872,10 +874,10 @@
           <t>RU000A1070X5</t>
         </is>
       </c>
-      <c r="C2" s="19" t="n">
+      <c r="C2" s="26" t="n">
         <v>46295</v>
       </c>
-      <c r="D2" s="20" t="n">
+      <c r="D2" s="27" t="n">
         <v>39200</v>
       </c>
     </row>
@@ -890,10 +892,10 @@
           <t>RU000A103QK3</t>
         </is>
       </c>
-      <c r="C3" s="19" t="n">
+      <c r="C3" s="26" t="n">
         <v>46280</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="27" t="n">
         <v>9453.6</v>
       </c>
     </row>
@@ -908,10 +910,10 @@
           <t>RU000A103QK3</t>
         </is>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C4" s="26" t="n">
         <v>46280</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="27" t="n">
         <v>240000</v>
       </c>
     </row>
@@ -926,10 +928,10 @@
           <t>RU000A106TM6</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="26" t="n">
         <v>46266</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="27" t="n">
         <v>201000</v>
       </c>
     </row>
@@ -944,10 +946,10 @@
           <t>RU000A10AHE5</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="26" t="n">
         <v>46252</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="27" t="n">
         <v>4113.2</v>
       </c>
     </row>
@@ -962,10 +964,10 @@
           <t>RU000A10AHE5</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="26" t="n">
         <v>46372</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="27" t="n">
         <v>182000</v>
       </c>
     </row>
@@ -980,10 +982,10 @@
           <t>RU000A106R95</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="26" t="n">
         <v>46248</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="27" t="n">
         <v>14789.36</v>
       </c>
     </row>
@@ -998,10 +1000,10 @@
           <t>RU000A106R95</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="26" t="n">
         <v>46248</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="27" t="n">
         <v>223000</v>
       </c>
     </row>
@@ -1009,7 +1011,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Данные автоматически обновлены 27.07.2026 в 13:29:51</t>
+          <t>Данные автоматически обновлены 27.07.2026 в 15:15:09</t>
         </is>
       </c>
     </row>
